--- a/01_analyses_states/Jammu and Kashmir/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Jammu and Kashmir/results/SoIB_summaries.xlsx
@@ -476,7 +476,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C8">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>2</v>

--- a/01_analyses_states/Jammu and Kashmir/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Jammu and Kashmir/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -414,7 +414,7 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>0</v>
       </c>
     </row>
@@ -425,13 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -446,7 +446,7 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="D5">
         <v>0</v>
       </c>
     </row>
@@ -462,7 +462,7 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="D6">
         <v>0</v>
       </c>
     </row>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C8">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3">
@@ -678,7 +678,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2">
-        <v>78.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2">
-        <v>83.5</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>21.4</v>
+        <v>23.3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>16.5</v>
+        <v>20.2</v>
       </c>
     </row>
   </sheetData>
